--- a/Models/Яйца/Датасет по яйцам wide.xlsx
+++ b/Models/Яйца/Датасет по яйцам wide.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7877,6 +7877,475 @@
         <v>19576.8</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>54329</v>
+      </c>
+      <c r="C122" t="n">
+        <v>20148.6</v>
+      </c>
+      <c r="D122" t="n">
+        <v>41510.5</v>
+      </c>
+      <c r="E122" t="n">
+        <v>4789.5</v>
+      </c>
+      <c r="F122" t="n">
+        <v>2154.3</v>
+      </c>
+      <c r="G122" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I122" t="n">
+        <v>15993</v>
+      </c>
+      <c r="J122" t="n">
+        <v>4617.9</v>
+      </c>
+      <c r="K122" t="n">
+        <v>8763.4</v>
+      </c>
+      <c r="L122" t="n">
+        <v>50601.1</v>
+      </c>
+      <c r="M122" t="n">
+        <v>33270.7</v>
+      </c>
+      <c r="N122" t="n">
+        <v>259</v>
+      </c>
+      <c r="O122" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="P122" t="n">
+        <v>2149</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>25193.8</v>
+      </c>
+      <c r="R122" t="n">
+        <v>1621.8</v>
+      </c>
+      <c r="S122" t="n">
+        <v>15255.1</v>
+      </c>
+      <c r="T122" t="n">
+        <v>47327</v>
+      </c>
+      <c r="U122" t="n">
+        <v>18830.5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>45131.6</v>
+      </c>
+      <c r="C123" t="n">
+        <v>17195.1</v>
+      </c>
+      <c r="D123" t="n">
+        <v>38920.1</v>
+      </c>
+      <c r="E123" t="n">
+        <v>4333.4</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2920.8</v>
+      </c>
+      <c r="G123" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I123" t="n">
+        <v>15508.6</v>
+      </c>
+      <c r="J123" t="n">
+        <v>4184.4</v>
+      </c>
+      <c r="K123" t="n">
+        <v>10359.5</v>
+      </c>
+      <c r="L123" t="n">
+        <v>41905.6</v>
+      </c>
+      <c r="M123" t="n">
+        <v>25198</v>
+      </c>
+      <c r="N123" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="O123" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="P123" t="n">
+        <v>3322.2</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>28661.9</v>
+      </c>
+      <c r="R123" t="n">
+        <v>1907.1</v>
+      </c>
+      <c r="S123" t="n">
+        <v>13505.1</v>
+      </c>
+      <c r="T123" t="n">
+        <v>44265.4</v>
+      </c>
+      <c r="U123" t="n">
+        <v>16545.6</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>60384.8</v>
+      </c>
+      <c r="C124" t="n">
+        <v>19281.6</v>
+      </c>
+      <c r="D124" t="n">
+        <v>41024.7</v>
+      </c>
+      <c r="E124" t="n">
+        <v>4701.3</v>
+      </c>
+      <c r="F124" t="n">
+        <v>3721</v>
+      </c>
+      <c r="G124" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I124" t="n">
+        <v>19010</v>
+      </c>
+      <c r="J124" t="n">
+        <v>6278</v>
+      </c>
+      <c r="K124" t="n">
+        <v>10459.2</v>
+      </c>
+      <c r="L124" t="n">
+        <v>46816.9</v>
+      </c>
+      <c r="M124" t="n">
+        <v>28343.3</v>
+      </c>
+      <c r="N124" t="n">
+        <v>427.2</v>
+      </c>
+      <c r="O124" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="P124" t="n">
+        <v>4423.2</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>27089.7</v>
+      </c>
+      <c r="R124" t="n">
+        <v>2712.3</v>
+      </c>
+      <c r="S124" t="n">
+        <v>14773.7</v>
+      </c>
+      <c r="T124" t="n">
+        <v>49073</v>
+      </c>
+      <c r="U124" t="n">
+        <v>21272.4</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>53061.5</v>
+      </c>
+      <c r="C125" t="n">
+        <v>19471.9</v>
+      </c>
+      <c r="D125" t="n">
+        <v>40330.8</v>
+      </c>
+      <c r="E125" t="n">
+        <v>4444.1</v>
+      </c>
+      <c r="F125" t="n">
+        <v>4525.3</v>
+      </c>
+      <c r="G125" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I125" t="n">
+        <v>18345.7</v>
+      </c>
+      <c r="J125" t="n">
+        <v>6696</v>
+      </c>
+      <c r="K125" t="n">
+        <v>11136.5</v>
+      </c>
+      <c r="L125" t="n">
+        <v>54373.40000000001</v>
+      </c>
+      <c r="M125" t="n">
+        <v>34878.5</v>
+      </c>
+      <c r="N125" t="n">
+        <v>681.7</v>
+      </c>
+      <c r="O125" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="P125" t="n">
+        <v>5159.2</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>29787.1</v>
+      </c>
+      <c r="R125" t="n">
+        <v>2117.5</v>
+      </c>
+      <c r="S125" t="n">
+        <v>16632.7</v>
+      </c>
+      <c r="T125" t="n">
+        <v>52808.8</v>
+      </c>
+      <c r="U125" t="n">
+        <v>23757.1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>62239.8</v>
+      </c>
+      <c r="C126" t="n">
+        <v>19921.5</v>
+      </c>
+      <c r="D126" t="n">
+        <v>42775.49999999999</v>
+      </c>
+      <c r="E126" t="n">
+        <v>4447.7</v>
+      </c>
+      <c r="F126" t="n">
+        <v>6128.1</v>
+      </c>
+      <c r="G126" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I126" t="n">
+        <v>20423.9</v>
+      </c>
+      <c r="J126" t="n">
+        <v>6999.2</v>
+      </c>
+      <c r="K126" t="n">
+        <v>10509</v>
+      </c>
+      <c r="L126" t="n">
+        <v>54243.7</v>
+      </c>
+      <c r="M126" t="n">
+        <v>35445.3</v>
+      </c>
+      <c r="N126" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="O126" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="P126" t="n">
+        <v>5802.4</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>27042.1</v>
+      </c>
+      <c r="R126" t="n">
+        <v>2241.9</v>
+      </c>
+      <c r="S126" t="n">
+        <v>16201</v>
+      </c>
+      <c r="T126" t="n">
+        <v>57261.1</v>
+      </c>
+      <c r="U126" t="n">
+        <v>25319.1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>61806.39999999999</v>
+      </c>
+      <c r="C127" t="n">
+        <v>19866.6</v>
+      </c>
+      <c r="D127" t="n">
+        <v>38080.09999999999</v>
+      </c>
+      <c r="E127" t="n">
+        <v>4083.3</v>
+      </c>
+      <c r="F127" t="n">
+        <v>6290.9</v>
+      </c>
+      <c r="G127" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I127" t="n">
+        <v>20916.3</v>
+      </c>
+      <c r="J127" t="n">
+        <v>10690.5</v>
+      </c>
+      <c r="K127" t="n">
+        <v>13037.6</v>
+      </c>
+      <c r="L127" t="n">
+        <v>56042.2</v>
+      </c>
+      <c r="M127" t="n">
+        <v>33353.5</v>
+      </c>
+      <c r="N127" t="n">
+        <v>837.8000000000001</v>
+      </c>
+      <c r="O127" t="n">
+        <v>88</v>
+      </c>
+      <c r="P127" t="n">
+        <v>6556.6</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>28008.8</v>
+      </c>
+      <c r="R127" t="n">
+        <v>4710.8</v>
+      </c>
+      <c r="S127" t="n">
+        <v>16699.6</v>
+      </c>
+      <c r="T127" t="n">
+        <v>59281.5</v>
+      </c>
+      <c r="U127" t="n">
+        <v>27352.3</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>62214.8</v>
+      </c>
+      <c r="C128" t="n">
+        <v>21013.7</v>
+      </c>
+      <c r="D128" t="n">
+        <v>34238.1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>3883.1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>6076.400000000001</v>
+      </c>
+      <c r="G128" t="n">
+        <v>14</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I128" t="n">
+        <v>21832</v>
+      </c>
+      <c r="J128" t="n">
+        <v>13810</v>
+      </c>
+      <c r="K128" t="n">
+        <v>11245.8</v>
+      </c>
+      <c r="L128" t="n">
+        <v>54984.8</v>
+      </c>
+      <c r="M128" t="n">
+        <v>32197.3</v>
+      </c>
+      <c r="N128" t="n">
+        <v>808.9</v>
+      </c>
+      <c r="O128" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="P128" t="n">
+        <v>7458.2</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>27987.2</v>
+      </c>
+      <c r="R128" t="n">
+        <v>2247.1</v>
+      </c>
+      <c r="S128" t="n">
+        <v>18734.2</v>
+      </c>
+      <c r="T128" t="n">
+        <v>63008.60000000001</v>
+      </c>
+      <c r="U128" t="n">
+        <v>23460.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
